--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.61708892141531</v>
+        <v>2.862776949729987</v>
       </c>
       <c r="D2" t="n">
-        <v>8.923284148787374</v>
+        <v>1.450033674177948</v>
       </c>
       <c r="E2" t="n">
-        <v>20.3933398345601</v>
+        <v>3.313917723116016</v>
       </c>
       <c r="F2" t="n">
-        <v>26.77912386607452</v>
+        <v>4.351607628237111</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.66328904367622</v>
+        <v>5.307784469597387</v>
       </c>
       <c r="D3" t="n">
-        <v>32.645027981231</v>
+        <v>5.304817046950037</v>
       </c>
       <c r="E3" t="n">
-        <v>20.3933398345601</v>
+        <v>3.313917723116016</v>
       </c>
       <c r="F3" t="n">
-        <v>26.77912386607452</v>
+        <v>4.351607628237111</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.26081275629703</v>
+        <v>11.41738207289827</v>
       </c>
       <c r="D4" t="n">
-        <v>73.88861800976203</v>
+        <v>12.00690042658633</v>
       </c>
       <c r="E4" t="n">
-        <v>20.3933398345601</v>
+        <v>3.313917723116016</v>
       </c>
       <c r="F4" t="n">
-        <v>26.77912386607452</v>
+        <v>4.351607628237111</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.22666512889326</v>
+        <v>9.136833083445154</v>
       </c>
       <c r="D5" t="n">
-        <v>69.19002777805633</v>
+        <v>11.24337951393415</v>
       </c>
       <c r="E5" t="n">
-        <v>20.3933398345601</v>
+        <v>3.313917723116016</v>
       </c>
       <c r="F5" t="n">
-        <v>26.77912386607452</v>
+        <v>4.351607628237111</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
